--- a/content/entries/death-cause-by-age/UnderlyingCauseOfDeath2018-2024-newCategoriesSORTED.xlsx
+++ b/content/entries/death-cause-by-age/UnderlyingCauseOfDeath2018-2024-newCategoriesSORTED.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4558" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4558" uniqueCount="133">
   <si>
     <t xml:space="preserve">ICD Chapter</t>
   </si>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">&lt; 1 year</t>
   </si>
   <si>
-    <t xml:space="preserve">Conditions from first year of birth</t>
+    <t xml:space="preserve">Pregnancy and Birth Complications</t>
   </si>
   <si>
     <t xml:space="preserve">1 year</t>
@@ -416,9 +416,6 @@
   </si>
   <si>
     <t xml:space="preserve">Maternal pregnancy complications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pregnancy complications</t>
   </si>
   <si>
     <t xml:space="preserve">Symptoms, signs and abnormal clinical and laboratory findings, not elsewhere classified</t>
@@ -1224,11 +1221,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="8550940"/>
-        <c:axId val="11330576"/>
+        <c:axId val="5767728"/>
+        <c:axId val="53972143"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="8550940"/>
+        <c:axId val="5767728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1280,12 +1277,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11330576"/>
+        <c:crossAx val="53972143"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="11330576"/>
+        <c:axId val="53972143"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1337,7 +1334,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8550940"/>
+        <c:crossAx val="5767728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1607,9 +1604,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>726120</xdr:colOff>
+      <xdr:colOff>725760</xdr:colOff>
       <xdr:row>1344</xdr:row>
-      <xdr:rowOff>75600</xdr:rowOff>
+      <xdr:rowOff>75240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1618,7 +1615,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8185320" y="264690360"/>
-        <a:ext cx="6129720" cy="4218840"/>
+        <a:ext cx="6129360" cy="4218480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -42512,7 +42509,7 @@
     </row>
     <row r="1566" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1566" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1566" s="1" t="s">
         <v>28</v>
@@ -42538,7 +42535,7 @@
     </row>
     <row r="1567" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1567" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1567" s="1" t="s">
         <v>26</v>
@@ -42564,7 +42561,7 @@
     </row>
     <row r="1568" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1568" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1568" s="1" t="s">
         <v>29</v>
@@ -42590,7 +42587,7 @@
     </row>
     <row r="1569" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1569" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1569" s="1" t="s">
         <v>30</v>
@@ -42616,7 +42613,7 @@
     </row>
     <row r="1570" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1570" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1570" s="1" t="s">
         <v>31</v>
@@ -42642,7 +42639,7 @@
     </row>
     <row r="1571" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1571" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1571" s="1" t="s">
         <v>32</v>
@@ -42668,7 +42665,7 @@
     </row>
     <row r="1572" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1572" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1572" s="1" t="s">
         <v>33</v>
@@ -42694,7 +42691,7 @@
     </row>
     <row r="1573" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1573" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1573" s="1" t="s">
         <v>34</v>
@@ -42720,7 +42717,7 @@
     </row>
     <row r="1574" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1574" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1574" s="1" t="s">
         <v>35</v>
@@ -42746,7 +42743,7 @@
     </row>
     <row r="1575" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1575" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1575" s="1" t="s">
         <v>36</v>
@@ -42772,7 +42769,7 @@
     </row>
     <row r="1576" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1576" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1576" s="1" t="s">
         <v>37</v>
@@ -42798,7 +42795,7 @@
     </row>
     <row r="1577" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1577" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1577" s="1" t="s">
         <v>38</v>
@@ -42824,7 +42821,7 @@
     </row>
     <row r="1578" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1578" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1578" s="1" t="s">
         <v>39</v>
@@ -42850,7 +42847,7 @@
     </row>
     <row r="1579" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1579" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1579" s="1" t="s">
         <v>40</v>
@@ -42876,7 +42873,7 @@
     </row>
     <row r="1580" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1580" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1580" s="1" t="s">
         <v>41</v>
@@ -42902,7 +42899,7 @@
     </row>
     <row r="1581" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1581" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1581" s="1" t="s">
         <v>42</v>
@@ -42928,7 +42925,7 @@
     </row>
     <row r="1582" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1582" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1582" s="1" t="s">
         <v>43</v>
@@ -42954,7 +42951,7 @@
     </row>
     <row r="1583" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1583" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1583" s="1" t="s">
         <v>44</v>
@@ -42980,7 +42977,7 @@
     </row>
     <row r="1584" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1584" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1584" s="1" t="s">
         <v>45</v>
@@ -43006,7 +43003,7 @@
     </row>
     <row r="1585" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1585" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1585" s="1" t="s">
         <v>46</v>
@@ -43032,7 +43029,7 @@
     </row>
     <row r="1586" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1586" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1586" s="1" t="s">
         <v>47</v>
@@ -43058,7 +43055,7 @@
     </row>
     <row r="1587" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1587" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1587" s="1" t="s">
         <v>48</v>
@@ -43084,7 +43081,7 @@
     </row>
     <row r="1588" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1588" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1588" s="1" t="s">
         <v>49</v>
@@ -43110,7 +43107,7 @@
     </row>
     <row r="1589" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1589" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1589" s="1" t="s">
         <v>50</v>
@@ -43136,7 +43133,7 @@
     </row>
     <row r="1590" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1590" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1590" s="1" t="s">
         <v>51</v>
@@ -43162,7 +43159,7 @@
     </row>
     <row r="1591" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1591" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1591" s="1" t="s">
         <v>52</v>
@@ -43188,7 +43185,7 @@
     </row>
     <row r="1592" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1592" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1592" s="1" t="s">
         <v>53</v>
@@ -43214,7 +43211,7 @@
     </row>
     <row r="1593" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1593" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1593" s="1" t="s">
         <v>54</v>
@@ -43240,7 +43237,7 @@
     </row>
     <row r="1594" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1594" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1594" s="1" t="s">
         <v>55</v>
@@ -43266,7 +43263,7 @@
     </row>
     <row r="1595" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1595" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1595" s="1" t="s">
         <v>56</v>
@@ -43292,7 +43289,7 @@
     </row>
     <row r="1596" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1596" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1596" s="1" t="s">
         <v>57</v>
@@ -43318,7 +43315,7 @@
     </row>
     <row r="1597" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1597" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1597" s="1" t="s">
         <v>58</v>
@@ -43344,7 +43341,7 @@
     </row>
     <row r="1598" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1598" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1598" s="1" t="s">
         <v>59</v>
@@ -43370,7 +43367,7 @@
     </row>
     <row r="1599" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1599" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1599" s="1" t="s">
         <v>61</v>
@@ -43396,7 +43393,7 @@
     </row>
     <row r="1600" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1600" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1600" s="1" t="s">
         <v>9</v>
@@ -43422,7 +43419,7 @@
     </row>
     <row r="1601" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1601" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1601" s="1" t="s">
         <v>11</v>
@@ -43448,7 +43445,7 @@
     </row>
     <row r="1602" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1602" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1602" s="1" t="s">
         <v>12</v>
@@ -43474,7 +43471,7 @@
     </row>
     <row r="1603" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1603" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1603" s="1" t="s">
         <v>13</v>
@@ -43500,7 +43497,7 @@
     </row>
     <row r="1604" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1604" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1604" s="1" t="s">
         <v>14</v>
@@ -43526,7 +43523,7 @@
     </row>
     <row r="1605" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1605" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1605" s="1" t="s">
         <v>15</v>
@@ -43552,7 +43549,7 @@
     </row>
     <row r="1606" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1606" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1606" s="1" t="s">
         <v>16</v>
@@ -43578,7 +43575,7 @@
     </row>
     <row r="1607" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1607" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1607" s="1" t="s">
         <v>17</v>
@@ -43604,7 +43601,7 @@
     </row>
     <row r="1608" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1608" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1608" s="1" t="s">
         <v>18</v>
@@ -43630,7 +43627,7 @@
     </row>
     <row r="1609" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1609" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1609" s="1" t="s">
         <v>19</v>
@@ -43656,7 +43653,7 @@
     </row>
     <row r="1610" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1610" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1610" s="1" t="s">
         <v>20</v>
@@ -43682,7 +43679,7 @@
     </row>
     <row r="1611" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1611" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1611" s="1" t="s">
         <v>21</v>
@@ -43708,7 +43705,7 @@
     </row>
     <row r="1612" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1612" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1612" s="1" t="s">
         <v>22</v>
@@ -43734,7 +43731,7 @@
     </row>
     <row r="1613" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1613" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1613" s="1" t="s">
         <v>23</v>
@@ -43760,7 +43757,7 @@
     </row>
     <row r="1614" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1614" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1614" s="1" t="s">
         <v>24</v>
@@ -43786,7 +43783,7 @@
     </row>
     <row r="1615" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1615" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1615" s="1" t="s">
         <v>25</v>
@@ -43812,7 +43809,7 @@
     </row>
     <row r="1616" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1616" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1616" s="1" t="s">
         <v>28</v>
@@ -43838,7 +43835,7 @@
     </row>
     <row r="1617" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1617" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1617" s="1" t="s">
         <v>26</v>
@@ -43864,7 +43861,7 @@
     </row>
     <row r="1618" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1618" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1618" s="1" t="s">
         <v>29</v>
@@ -43890,7 +43887,7 @@
     </row>
     <row r="1619" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1619" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1619" s="1" t="s">
         <v>30</v>
@@ -43916,7 +43913,7 @@
     </row>
     <row r="1620" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1620" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1620" s="1" t="s">
         <v>31</v>
@@ -43942,7 +43939,7 @@
     </row>
     <row r="1621" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1621" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1621" s="1" t="s">
         <v>32</v>
@@ -43968,7 +43965,7 @@
     </row>
     <row r="1622" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1622" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1622" s="1" t="s">
         <v>33</v>
@@ -43994,7 +43991,7 @@
     </row>
     <row r="1623" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1623" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1623" s="1" t="s">
         <v>34</v>
@@ -44020,7 +44017,7 @@
     </row>
     <row r="1624" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1624" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1624" s="1" t="s">
         <v>35</v>
@@ -44046,7 +44043,7 @@
     </row>
     <row r="1625" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1625" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1625" s="1" t="s">
         <v>36</v>
@@ -44072,7 +44069,7 @@
     </row>
     <row r="1626" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1626" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1626" s="1" t="s">
         <v>37</v>
@@ -44098,7 +44095,7 @@
     </row>
     <row r="1627" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1627" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1627" s="1" t="s">
         <v>38</v>
@@ -44124,7 +44121,7 @@
     </row>
     <row r="1628" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1628" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1628" s="1" t="s">
         <v>39</v>
@@ -44150,7 +44147,7 @@
     </row>
     <row r="1629" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1629" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1629" s="1" t="s">
         <v>40</v>
@@ -44176,7 +44173,7 @@
     </row>
     <row r="1630" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1630" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1630" s="1" t="s">
         <v>41</v>
@@ -44202,7 +44199,7 @@
     </row>
     <row r="1631" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1631" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1631" s="1" t="s">
         <v>42</v>
@@ -44228,7 +44225,7 @@
     </row>
     <row r="1632" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1632" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1632" s="1" t="s">
         <v>43</v>
@@ -44254,7 +44251,7 @@
     </row>
     <row r="1633" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1633" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1633" s="1" t="s">
         <v>44</v>
@@ -44280,7 +44277,7 @@
     </row>
     <row r="1634" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1634" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1634" s="1" t="s">
         <v>45</v>
@@ -44306,7 +44303,7 @@
     </row>
     <row r="1635" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1635" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1635" s="1" t="s">
         <v>46</v>
@@ -44332,7 +44329,7 @@
     </row>
     <row r="1636" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1636" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1636" s="1" t="s">
         <v>47</v>
@@ -44358,7 +44355,7 @@
     </row>
     <row r="1637" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1637" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1637" s="1" t="s">
         <v>48</v>
@@ -44384,7 +44381,7 @@
     </row>
     <row r="1638" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1638" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1638" s="1" t="s">
         <v>49</v>
@@ -44410,7 +44407,7 @@
     </row>
     <row r="1639" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1639" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1639" s="1" t="s">
         <v>50</v>
@@ -44436,7 +44433,7 @@
     </row>
     <row r="1640" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1640" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1640" s="1" t="s">
         <v>51</v>
@@ -44462,7 +44459,7 @@
     </row>
     <row r="1641" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1641" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1641" s="1" t="s">
         <v>52</v>
@@ -44488,7 +44485,7 @@
     </row>
     <row r="1642" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1642" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1642" s="1" t="s">
         <v>53</v>
@@ -44514,7 +44511,7 @@
     </row>
     <row r="1643" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1643" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1643" s="1" t="s">
         <v>54</v>
@@ -44540,7 +44537,7 @@
     </row>
     <row r="1644" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1644" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1644" s="1" t="s">
         <v>55</v>
@@ -44566,7 +44563,7 @@
     </row>
     <row r="1645" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1645" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1645" s="1" t="s">
         <v>56</v>
@@ -44592,7 +44589,7 @@
     </row>
     <row r="1646" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1646" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1646" s="1" t="s">
         <v>57</v>
@@ -44618,7 +44615,7 @@
     </row>
     <row r="1647" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1647" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1647" s="1" t="s">
         <v>58</v>
@@ -44644,7 +44641,7 @@
     </row>
     <row r="1648" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1648" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1648" s="1" t="s">
         <v>59</v>
@@ -44670,7 +44667,7 @@
     </row>
     <row r="1649" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1649" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1649" s="1" t="s">
         <v>60</v>
@@ -44696,7 +44693,7 @@
     </row>
     <row r="1650" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1650" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1650" s="1" t="s">
         <v>61</v>
@@ -44722,7 +44719,7 @@
     </row>
     <row r="1651" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1651" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1651" s="1" t="s">
         <v>62</v>
@@ -44748,7 +44745,7 @@
     </row>
     <row r="1652" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1652" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1652" s="1" t="s">
         <v>63</v>
@@ -44774,7 +44771,7 @@
     </row>
     <row r="1653" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1653" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1653" s="1" t="s">
         <v>64</v>
@@ -44800,7 +44797,7 @@
     </row>
     <row r="1654" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1654" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1654" s="1" t="s">
         <v>65</v>
@@ -44826,7 +44823,7 @@
     </row>
     <row r="1655" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1655" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1655" s="1" t="s">
         <v>66</v>
@@ -44852,7 +44849,7 @@
     </row>
     <row r="1656" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1656" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1656" s="1" t="s">
         <v>67</v>
@@ -44878,7 +44875,7 @@
     </row>
     <row r="1657" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1657" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1657" s="1" t="s">
         <v>68</v>
@@ -44904,7 +44901,7 @@
     </row>
     <row r="1658" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1658" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1658" s="1" t="s">
         <v>69</v>
@@ -44930,7 +44927,7 @@
     </row>
     <row r="1659" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1659" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1659" s="1" t="s">
         <v>70</v>
@@ -44956,7 +44953,7 @@
     </row>
     <row r="1660" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1660" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1660" s="1" t="s">
         <v>71</v>
@@ -44982,7 +44979,7 @@
     </row>
     <row r="1661" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1661" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1661" s="1" t="s">
         <v>72</v>
@@ -45008,7 +45005,7 @@
     </row>
     <row r="1662" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1662" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1662" s="1" t="s">
         <v>73</v>
@@ -45034,7 +45031,7 @@
     </row>
     <row r="1663" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1663" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1663" s="1" t="s">
         <v>74</v>
@@ -45060,7 +45057,7 @@
     </row>
     <row r="1664" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1664" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1664" s="1" t="s">
         <v>75</v>
@@ -45086,7 +45083,7 @@
     </row>
     <row r="1665" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1665" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1665" s="1" t="s">
         <v>76</v>
@@ -45112,7 +45109,7 @@
     </row>
     <row r="1666" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1666" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1666" s="1" t="s">
         <v>77</v>
@@ -45138,7 +45135,7 @@
     </row>
     <row r="1667" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1667" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1667" s="1" t="s">
         <v>78</v>
@@ -45164,7 +45161,7 @@
     </row>
     <row r="1668" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1668" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1668" s="1" t="s">
         <v>79</v>
@@ -45190,7 +45187,7 @@
     </row>
     <row r="1669" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1669" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1669" s="1" t="s">
         <v>80</v>
@@ -45216,7 +45213,7 @@
     </row>
     <row r="1670" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1670" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1670" s="1" t="s">
         <v>81</v>
@@ -45242,7 +45239,7 @@
     </row>
     <row r="1671" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1671" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1671" s="1" t="s">
         <v>82</v>
@@ -45268,7 +45265,7 @@
     </row>
     <row r="1672" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1672" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1672" s="1" t="s">
         <v>83</v>
@@ -45294,7 +45291,7 @@
     </row>
     <row r="1673" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1673" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1673" s="1" t="s">
         <v>84</v>
@@ -45320,7 +45317,7 @@
     </row>
     <row r="1674" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1674" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1674" s="1" t="s">
         <v>85</v>
@@ -45346,7 +45343,7 @@
     </row>
     <row r="1675" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1675" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1675" s="1" t="s">
         <v>86</v>
@@ -45372,7 +45369,7 @@
     </row>
     <row r="1676" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1676" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1676" s="1" t="s">
         <v>87</v>
@@ -45398,7 +45395,7 @@
     </row>
     <row r="1677" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1677" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1677" s="1" t="s">
         <v>88</v>
@@ -45424,7 +45421,7 @@
     </row>
     <row r="1678" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1678" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1678" s="1" t="s">
         <v>89</v>
@@ -45450,7 +45447,7 @@
     </row>
     <row r="1679" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1679" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1679" s="1" t="s">
         <v>90</v>
@@ -45476,7 +45473,7 @@
     </row>
     <row r="1680" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1680" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1680" s="1" t="s">
         <v>91</v>
@@ -45502,7 +45499,7 @@
     </row>
     <row r="1681" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1681" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1681" s="1" t="s">
         <v>92</v>
@@ -45528,7 +45525,7 @@
     </row>
     <row r="1682" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1682" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1682" s="1" t="s">
         <v>93</v>
@@ -45554,7 +45551,7 @@
     </row>
     <row r="1683" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1683" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1683" s="1" t="s">
         <v>94</v>
@@ -45580,7 +45577,7 @@
     </row>
     <row r="1684" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1684" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1684" s="1" t="s">
         <v>95</v>
@@ -45606,7 +45603,7 @@
     </row>
     <row r="1685" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1685" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1685" s="1" t="s">
         <v>96</v>
@@ -45632,7 +45629,7 @@
     </row>
     <row r="1686" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1686" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1686" s="1" t="s">
         <v>98</v>
@@ -45658,7 +45655,7 @@
     </row>
     <row r="1687" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1687" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1687" s="1" t="s">
         <v>99</v>
@@ -45684,7 +45681,7 @@
     </row>
     <row r="1688" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1688" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1688" s="1" t="s">
         <v>100</v>
@@ -45710,7 +45707,7 @@
     </row>
     <row r="1689" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1689" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1689" s="1" t="s">
         <v>101</v>
@@ -45736,7 +45733,7 @@
     </row>
     <row r="1690" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1690" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1690" s="1" t="s">
         <v>102</v>
@@ -45762,7 +45759,7 @@
     </row>
     <row r="1691" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1691" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1691" s="1" t="s">
         <v>103</v>
@@ -45788,7 +45785,7 @@
     </row>
     <row r="1692" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1692" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1692" s="1" t="s">
         <v>104</v>
@@ -45814,7 +45811,7 @@
     </row>
     <row r="1693" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1693" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1693" s="1" t="s">
         <v>105</v>
@@ -45840,7 +45837,7 @@
     </row>
     <row r="1694" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1694" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1694" s="1" t="s">
         <v>106</v>
@@ -45866,7 +45863,7 @@
     </row>
     <row r="1695" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1695" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1695" s="1" t="s">
         <v>107</v>
@@ -45892,7 +45889,7 @@
     </row>
     <row r="1696" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1696" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1696" s="1" t="s">
         <v>108</v>
@@ -45918,7 +45915,7 @@
     </row>
     <row r="1697" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1697" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1697" s="1" t="s">
         <v>109</v>
@@ -45944,7 +45941,7 @@
     </row>
     <row r="1698" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1698" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1698" s="1" t="s">
         <v>110</v>
@@ -45970,7 +45967,7 @@
     </row>
     <row r="1699" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1699" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1699" s="1" t="s">
         <v>111</v>
@@ -45996,7 +45993,7 @@
     </row>
     <row r="1700" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1700" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1700" s="1" t="s">
         <v>112</v>
@@ -46022,7 +46019,7 @@
     </row>
     <row r="1701" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1701" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1701" s="1" t="s">
         <v>113</v>
